--- a/客户分级跟进表_2026-09.xlsx
+++ b/客户分级跟进表_2026-09.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'A级-重点好跟进'!$A$1:$AA$86</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'B级-慢慢跟'!$A$1:$X$469</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'C级-难啃'!$A$1:$X$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'B级-慢慢跟'!$A$1:$X$471</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'C级-难啃'!$A$1:$X$154</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -10171,7 +10171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X469"/>
+  <dimension ref="A1:X471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -20281,7 +20281,7 @@
       <c r="P108" s="3" t="inlineStr"/>
       <c r="Q108" s="3" t="inlineStr">
         <is>
-          <t>Oxfordshire</t>
+          <t>Oxfordshire；【2026-09-22 补】官网列 Netonix WISP 交换机（PoE、宽温、DC 输入）为代理品牌。</t>
         </is>
       </c>
       <c r="R108" s="3" t="inlineStr">
@@ -20291,17 +20291,17 @@
       </c>
       <c r="S108" s="3" t="inlineStr">
         <is>
-          <t>通用分销商信号，无差异化切入点，慢慢跟</t>
+          <t>有信号（交换专长、PoE/监控/门禁、ISP/骨干）但需先验证需求或联系人不具体</t>
         </is>
       </c>
       <c r="T108" s="3" t="inlineStr">
         <is>
-          <t>待摸底</t>
+          <t>PoE/监控/门禁</t>
         </is>
       </c>
       <c r="U108" s="3" t="inlineStr">
         <is>
-          <t>保持低频联系，等他出现交换机需求信号再跟进</t>
+          <t>先问他在做什么监控项目、多大功率，用小批量试单切入</t>
         </is>
       </c>
       <c r="V108" s="3" t="inlineStr"/>
@@ -54734,8 +54734,196 @@
       <c r="W469" s="3" t="inlineStr"/>
       <c r="X469" s="3" t="inlineStr"/>
     </row>
+    <row r="470">
+      <c r="A470" s="3" t="inlineStr">
+        <is>
+          <t>Westbase Networks</t>
+        </is>
+      </c>
+      <c r="B470" s="3" t="inlineStr">
+        <is>
+          <t>英国</t>
+        </is>
+      </c>
+      <c r="C470" s="3" t="inlineStr"/>
+      <c r="D470" s="3" t="inlineStr">
+        <is>
+          <t>eu.westbase.io</t>
+        </is>
+      </c>
+      <c r="E470" s="3" t="inlineStr">
+        <is>
+          <t>分销（Netonix 官方）</t>
+        </is>
+      </c>
+      <c r="F470" s="3" t="inlineStr">
+        <is>
+          <t>Netonix（WISP PoE 交换机）</t>
+        </is>
+      </c>
+      <c r="G470" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H470" s="3" t="inlineStr">
+        <is>
+          <t>官方 Netonix 英国 + 欧洲分销，代理全系 WISP 交换机；手上有 Netonix 存量客户</t>
+        </is>
+      </c>
+      <c r="I470" s="3" t="inlineStr">
+        <is>
+          <t>LT-IS6312XGP-4XS8GT</t>
+        </is>
+      </c>
+      <c r="J470" s="3" t="inlineStr">
+        <is>
+          <t>官网 Contact 页</t>
+        </is>
+      </c>
+      <c r="K470" s="3" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="L470" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M470" s="3" t="inlineStr">
+        <is>
+          <t>Netonix/PLANET 经销商名录/2026-09</t>
+        </is>
+      </c>
+      <c r="N470" s="3" t="inlineStr"/>
+      <c r="O470" s="3" t="inlineStr"/>
+      <c r="P470" s="3" t="inlineStr"/>
+      <c r="Q470" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-22 新增】eu.westbase.io 自称 official Netonix UK and European distributor，代理 WISP Switch 全系。Netonix 为美式 WISP PoE 交换机（宽温、DC 输入）。</t>
+        </is>
+      </c>
+      <c r="R470" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S470" s="3" t="inlineStr">
+        <is>
+          <t>有信号（交换专长、PoE/监控/门禁、ISP/骨干）但需先验证需求或联系人不具体</t>
+        </is>
+      </c>
+      <c r="T470" s="3" t="inlineStr">
+        <is>
+          <t>PoE/监控/门禁</t>
+        </is>
+      </c>
+      <c r="U470" s="3" t="inlineStr">
+        <is>
+          <t>先问他在做什么监控项目、多大功率，用小批量试单切入</t>
+        </is>
+      </c>
+      <c r="V470" s="3" t="inlineStr"/>
+      <c r="W470" s="3" t="inlineStr"/>
+      <c r="X470" s="3" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="3" t="inlineStr">
+        <is>
+          <t>Netceed UK</t>
+        </is>
+      </c>
+      <c r="B471" s="3" t="inlineStr">
+        <is>
+          <t>英国</t>
+        </is>
+      </c>
+      <c r="C471" s="3" t="inlineStr"/>
+      <c r="D471" s="3" t="inlineStr">
+        <is>
+          <t>uk-store.netceed.com</t>
+        </is>
+      </c>
+      <c r="E471" s="3" t="inlineStr">
+        <is>
+          <t>分销（PLANET 授权）</t>
+        </is>
+      </c>
+      <c r="F471" s="3" t="inlineStr">
+        <is>
+          <t>PLANET 工业交换机</t>
+        </is>
+      </c>
+      <c r="G471" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H471" s="3" t="inlineStr">
+        <is>
+          <t>台厂 PLANET 工业线（DIN 导轨、宽温）英国渠道</t>
+        </is>
+      </c>
+      <c r="I471" s="3" t="inlineStr">
+        <is>
+          <t>LT-IS6312XGP-4XS8GT</t>
+        </is>
+      </c>
+      <c r="J471" s="3" t="inlineStr">
+        <is>
+          <t>官网 Contact 页</t>
+        </is>
+      </c>
+      <c r="K471" s="3" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="L471" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M471" s="3" t="inlineStr">
+        <is>
+          <t>Netonix/PLANET 经销商名录/2026-09</t>
+        </is>
+      </c>
+      <c r="N471" s="3" t="inlineStr"/>
+      <c r="O471" s="3" t="inlineStr"/>
+      <c r="P471" s="3" t="inlineStr"/>
+      <c r="Q471" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-22 新增】Netceed UK 商店在售 PLANET DIN 导轨工业交换机（IGS-10020HPT 8口270W PoE、IGS-4215-4P4T2S、IGS-501T 5口）。</t>
+        </is>
+      </c>
+      <c r="R471" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S471" s="3" t="inlineStr">
+        <is>
+          <t>有信号（交换专长、PoE/监控/门禁、工业/楼宇）但需先验证需求或联系人不具体</t>
+        </is>
+      </c>
+      <c r="T471" s="3" t="inlineStr">
+        <is>
+          <t>PoE/监控/门禁</t>
+        </is>
+      </c>
+      <c r="U471" s="3" t="inlineStr">
+        <is>
+          <t>先问他在做什么监控项目、多大功率，用小批量试单切入</t>
+        </is>
+      </c>
+      <c r="V471" s="3" t="inlineStr"/>
+      <c r="W471" s="3" t="inlineStr"/>
+      <c r="X471" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:X469"/>
+  <autoFilter ref="A1:X471"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -54746,7 +54934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X153"/>
+  <dimension ref="A1:X154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -59746,7 +59934,7 @@
       <c r="P53" s="3" t="inlineStr"/>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>Surrey；英国 Master 【关联】同集团另一实体：WiFi-Stock.com（JSC Katalita，立陶宛）（wifi-stock.com）</t>
+          <t>Surrey；英国 Master 【关联】同集团另一实体：WiFi-Stock.com（JSC Katalita，立陶宛）（wifi-stock.com）；【2026-09-22 补】官网列 Netonix WISP 交换机（PoE、宽温、DC 输入）为代理品牌。</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
@@ -62848,7 +63036,7 @@
       <c r="P86" s="3" t="inlineStr"/>
       <c r="Q86" s="3" t="inlineStr">
         <is>
-          <t>Kaunas 【关联】同集团另一实体：Wifi Stock (UK) Ltd（wifi-stock.co.uk）</t>
+          <t>Kaunas 【关联】同集团另一实体：Wifi Stock (UK) Ltd（wifi-stock.co.uk）；【2026-09-22 补】官网列 Netonix WISP 交换机（PoE、宽温、DC 输入）为代理品牌。</t>
         </is>
       </c>
       <c r="R86" s="3" t="inlineStr">
@@ -67724,7 +67912,7 @@
       <c r="P136" s="3" t="inlineStr"/>
       <c r="Q136" s="3" t="inlineStr">
         <is>
-          <t>LinITX 是英国 MikroTik Master Distributor + VAD + 认证培训中心，公司内有 3 位认证顾问：Jono Thompson（training@linitx.com，7 证含 MTCSWE，交换/VLAN/CAPsMAN/流量管理）；Joel Blakey（MikroTik@LinITX.com，技术销售工程师，有线无线设计与无线勘测）；Luke Cuddehay（shop@linitx.com，技术销售工程师）。同一电话 +44 1449 888000</t>
+          <t>LinITX 是英国 MikroTik Master Distributor + VAD + 认证培训中心，公司内有 3 位认证顾问：Jono Thompson（training@linitx.com，7 证含 MTCSWE，交换/VLAN/CAPsMAN/流量管理）；Joel Blakey（MikroTik@LinITX.com，技术销售工程师，有线无线设计与无线勘测）；Luke Cuddehay（shop@linitx.com，技术销售工程师）。同一电话 +44 1449 888000；【2026-09-22 补】官网列 Netonix WISP 交换机（PoE、宽温、DC 输入）为代理品牌。</t>
         </is>
       </c>
       <c r="R136" s="3" t="inlineStr">
@@ -69385,8 +69573,102 @@
       <c r="W153" s="3" t="inlineStr"/>
       <c r="X153" s="3" t="inlineStr"/>
     </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>Saratota</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>英国</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr"/>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>saratota.com</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>分销（PLANET 授权）</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>PLANET（台厂工业/商用交换机）</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>台厂 PLANET 的英国分销；台厂不是客户，其渠道才是目标</t>
+        </is>
+      </c>
+      <c r="I154" s="3" t="inlineStr">
+        <is>
+          <t>LT-IS6312XGP-4XS8GT</t>
+        </is>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>官网 Contact 页</t>
+        </is>
+      </c>
+      <c r="K154" s="3" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>Netonix/PLANET 经销商名录/2026-09</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr"/>
+      <c r="O154" s="3" t="inlineStr"/>
+      <c r="P154" s="3" t="inlineStr"/>
+      <c r="Q154" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-22 新增】saratota.com 页面标注 Planet Technology UK distributor / supplier，上架 PLANET 工业 PoE 与太阳能供电交换机。</t>
+        </is>
+      </c>
+      <c r="R154" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S154" s="3" t="inlineStr">
+        <is>
+          <t>集团/大公司/自有品牌/竞品/范围外，决策链长或存在品牌冲突</t>
+        </is>
+      </c>
+      <c r="T154" s="3" t="inlineStr">
+        <is>
+          <t>集团/大公司，决策链长，采购集中</t>
+        </is>
+      </c>
+      <c r="U154" s="3" t="inlineStr">
+        <is>
+          <t>先问清是国别决策还是集团统一采购；找准品类经理而非 CPO</t>
+        </is>
+      </c>
+      <c r="V154" s="3" t="inlineStr"/>
+      <c r="W154" s="3" t="inlineStr"/>
+      <c r="X154" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:X153"/>
+  <autoFilter ref="A1:X154"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/客户分级跟进表_2026-09.xlsx
+++ b/客户分级跟进表_2026-09.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'A级-重点好跟进'!$A$1:$AA$89</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'B级-慢慢跟'!$A$1:$X$492</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'B级-慢慢跟'!$A$1:$X$493</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'C级-难啃'!$A$1:$X$150</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -713,7 +713,7 @@
       <c r="P2" s="3" t="inlineStr"/>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>交通/公用事业/监控；【2026-09-22 补】经 EtherWAN（台厂，1996 年创立，现被德国 Phoenix Contact 收购）渠道名录确认为其分销商。站点明示经销 EtherWAN 加固型工业交换机（-40~+75℃、5–48 口、非网管/网管/三层）、90W PoE、光纤介质转换器与 VDSL2 延长器，面向交通、公用事业、IP 监控与关键基础设施；地址 Toddington, Bedfordshire。</t>
+          <t>交通/公用事业/监控；【2026-09-22 补】经 EtherWAN（台厂，1996 年创立，现被德国 Phoenix Contact 收购）渠道名录确认为其分销商。站点明示经销 EtherWAN 加固型工业交换机（-40~+75℃、5–48 口、非网管/网管/三层）、90W PoE、光纤介质转换器与 VDSL2 延长器，面向交通、公用事业、IP 监控与关键基础设施；地址 Toddington, Bedfordshire。；【2026-09-23】另经 Atop（台厂）渠道确认其为 Atop 英国分销商——串口服务器、Modbus/IEC 61850 协议网关、EN 50155 与 IEC 61850-3 交换机。</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
@@ -935,7 +935,7 @@
       <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>克拉科夫，波兰工业网络分销</t>
+          <t>克拉科夫，波兰工业网络分销；【2026-09-23】Antaira 官方 where-to-buy 名录确认的分销商。波兰分销商，另有 kontakt@csi.pl。</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
@@ -1044,7 +1044,7 @@
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>Porto Salvo，伊比利亚工业方案商</t>
+          <t>Porto Salvo，伊比利亚工业方案商；【2026-09-23】Antaira 官方 where-to-buy 名录确认的分销商。葡萄牙分销商。</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
@@ -1153,7 +1153,7 @@
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>Runcorn，英国工业网络分销</t>
+          <t>Runcorn，英国工业网络分销；【2026-09-23】Antaira 官方 where-to-buy 名录确认的分销商。英国分销商，另有 info@systemdevices.co.uk。</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
@@ -1262,7 +1262,7 @@
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>已验证：站内还在卖 B+B SmartWorx 全线 【范围外】不在本次目标区域（欧洲+美加）内，暂不触达，留档备用；【2026-09-22 补】经 Advantech（台厂）EKI 系列渠道确认为其分销商。站点有 Advantech EKI 工业以太网设备专区，共 440 个型号、153 个现货，含 EKI-2528-BE（€103）、EKI-5528I-AE（€160）、EKI-7712G-4FPI-BE（€298）、EKI-7720G-4FI-BU（€1,144）等，标价为中欧行情参考。</t>
+          <t>已验证：站内还在卖 B+B SmartWorx 全线 【范围外】不在本次目标区域（欧洲+美加）内，暂不触达，留档备用；【2026-09-22 补】经 Advantech（台厂）EKI 系列渠道确认为其分销商。站点有 Advantech EKI 工业以太网设备专区，共 440 个型号、153 个现货，含 EKI-2528-BE（€103）、EKI-5528I-AE（€160）、EKI-7712G-4FPI-BE（€298）、EKI-7720G-4FI-BU（€1,144）等，标价为中欧行情参考。；【2026-09-23】Westermo 官方 where-to-buy 名录确认的分销商。捷克与斯洛伐克双国 **Silver 分销商**（Westermo 渠道第二等级）。</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
@@ -1371,7 +1371,7 @@
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>荷兰工业数据通信分销</t>
+          <t>荷兰工业数据通信分销；【2026-09-23】Westermo 官方 where-to-buy 名录确认的分销商。荷兰 reseller，具备全套技术支持与本地办会能力。</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
@@ -10502,7 +10502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X492"/>
+  <dimension ref="A1:X493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -14840,7 +14840,7 @@
       <c r="P46" s="3" t="inlineStr"/>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>Pécel，中东欧增量市场</t>
+          <t>Pécel，中东欧增量市场；【2026-09-23】Antaira 官方 where-to-buy 名录确认的分销商。匈牙利分销商。</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
@@ -15028,7 +15028,7 @@
       <c r="P48" s="3" t="inlineStr"/>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>巴尔干，覆盖两国 【范围外】不在本次目标区域（欧洲+美加）内，暂不触达，留档备用</t>
+          <t>巴尔干，覆盖两国 【范围外】不在本次目标区域（欧洲+美加）内，暂不触达，留档备用；【2026-09-23】Westermo 官方 where-to-buy 名录确认的分销商。克罗地亚与斯洛文尼亚双国 Bronze 分销商。</t>
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr">
@@ -15210,7 +15210,11 @@
       <c r="N50" s="3" t="inlineStr"/>
       <c r="O50" s="3" t="inlineStr"/>
       <c r="P50" s="3" t="inlineStr"/>
-      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="Q50" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】Westermo 官方 where-to-buy 名录确认的分销商。保加利亚 reseller（本地库存）。</t>
+        </is>
+      </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -15486,7 +15490,7 @@
       <c r="P53" s="3" t="inlineStr"/>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>另有罗马尼亚分公司</t>
+          <t>另有罗马尼亚分公司；【2026-09-23】Westermo 官方 where-to-buy 名录确认的分销商。匈牙利 reseller（本地库存）。</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
@@ -15580,7 +15584,7 @@
       <c r="P54" s="3" t="inlineStr"/>
       <c r="Q54" s="3" t="inlineStr">
         <is>
-          <t>北欧小市场，竞争小</t>
+          <t>北欧小市场，竞争小；【2026-09-23】Westermo 官方 where-to-buy 名录确认的分销商。冰岛 reseller（本地库存）。</t>
         </is>
       </c>
       <c r="R54" s="3" t="inlineStr">
@@ -15672,7 +15676,11 @@
       <c r="N55" s="3" t="inlineStr"/>
       <c r="O55" s="3" t="inlineStr"/>
       <c r="P55" s="3" t="inlineStr"/>
-      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="Q55" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】Westermo 官方 where-to-buy 名录确认的分销商。以色列 reseller，具备认证技术支持与 Westermo 方案能力。</t>
+        </is>
+      </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -16044,7 +16052,11 @@
       <c r="N59" s="3" t="inlineStr"/>
       <c r="O59" s="3" t="inlineStr"/>
       <c r="P59" s="3" t="inlineStr"/>
-      <c r="Q59" s="3" t="inlineStr"/>
+      <c r="Q59" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】Westermo 官方 where-to-buy 名录确认的分销商。北马其顿 reseller（本地库存）。</t>
+        </is>
+      </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -16134,7 +16146,11 @@
       <c r="N60" s="3" t="inlineStr"/>
       <c r="O60" s="3" t="inlineStr"/>
       <c r="P60" s="3" t="inlineStr"/>
-      <c r="Q60" s="3" t="inlineStr"/>
+      <c r="Q60" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】Westermo 官方 where-to-buy 名录确认的分销商。马耳他 reseller，具备认证技术支持与 Westermo 方案能力。</t>
+        </is>
+      </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -16318,7 +16334,11 @@
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="3" t="inlineStr"/>
       <c r="P62" s="3" t="inlineStr"/>
-      <c r="Q62" s="3" t="inlineStr"/>
+      <c r="Q62" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】Westermo 官方 where-to-buy 名录确认的分销商。葡萄牙 reseller（本地库存）。</t>
+        </is>
+      </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -16594,7 +16614,7 @@
       <c r="P65" s="3" t="inlineStr"/>
       <c r="Q65" s="3" t="inlineStr">
         <is>
-          <t>贝尔格莱德</t>
+          <t>贝尔格莱德；【2026-09-23】Westermo 官方 where-to-buy 名录确认的分销商。塞尔维亚 reseller（本地库存）。</t>
         </is>
       </c>
       <c r="R65" s="3" t="inlineStr">
@@ -16688,7 +16708,7 @@
       <c r="P66" s="3" t="inlineStr"/>
       <c r="Q66" s="3" t="inlineStr">
         <is>
-          <t>体量大、流程长，优先级低</t>
+          <t>体量大、流程长，优先级低；【2026-09-23】Westermo 官方 where-to-buy 名录确认的分销商。西班牙 **Silver 分销商**。</t>
         </is>
       </c>
       <c r="R66" s="3" t="inlineStr">
@@ -16782,7 +16802,7 @@
       <c r="P67" s="3" t="inlineStr"/>
       <c r="Q67" s="3" t="inlineStr">
         <is>
-          <t>伊斯坦布尔</t>
+          <t>伊斯坦布尔；【2026-09-23】Westermo 官方 where-to-buy 名录确认的分销商。土耳其分销商（本地库存）。</t>
         </is>
       </c>
       <c r="R67" s="3" t="inlineStr">
@@ -57235,8 +57255,102 @@
       <c r="W492" s="3" t="inlineStr"/>
       <c r="X492" s="3" t="inlineStr"/>
     </row>
+    <row r="493">
+      <c r="A493" s="3" t="inlineStr">
+        <is>
+          <t>Adnan RIHAN</t>
+        </is>
+      </c>
+      <c r="B493" s="3" t="inlineStr">
+        <is>
+          <t>法国</t>
+        </is>
+      </c>
+      <c r="C493" s="3" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D493" s="3" t="inlineStr"/>
+      <c r="E493" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F493" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MTCNA / MTCIPv6E；IPv6 方向有专证</t>
+        </is>
+      </c>
+      <c r="G493" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H493" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I493" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328GP-4GX24GT-S</t>
+        </is>
+      </c>
+      <c r="J493" s="3" t="inlineStr">
+        <is>
+          <t>adnan+mikrotik@rihan.fr；+33 6 78 62 26 20</t>
+        </is>
+      </c>
+      <c r="K493" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L493" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M493" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N493" s="3" t="inlineStr"/>
+      <c r="O493" s="3" t="inlineStr"/>
+      <c r="P493" s="3" t="inlineStr"/>
+      <c r="Q493" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录（mikrotik.com/consultants）收录，含证书等级与直接联系方式。法国仅 2 位上榜顾问之一，驻巴黎。</t>
+        </is>
+      </c>
+      <c r="R493" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S493" s="3" t="inlineStr">
+        <is>
+          <t>通用分销商信号，无差异化切入点，慢慢跟</t>
+        </is>
+      </c>
+      <c r="T493" s="3" t="inlineStr">
+        <is>
+          <t>待摸底</t>
+        </is>
+      </c>
+      <c r="U493" s="3" t="inlineStr">
+        <is>
+          <t>保持低频联系，等他出现交换机需求信号再跟进</t>
+        </is>
+      </c>
+      <c r="V493" s="3" t="inlineStr"/>
+      <c r="W493" s="3" t="inlineStr"/>
+      <c r="X493" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:X492"/>
+  <autoFilter ref="A1:X493"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -59987,7 +60101,7 @@
       <c r="P29" s="3" t="inlineStr"/>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>华沙，自动化目录分销，SKU 量大；OEM Automatic 集团：瑞典 oemautomatic.se（自有品牌，OEM 优先）+ 捷克 oemautomatic.cz，一单谈三国 【关联】同集团另一实体：OEM Automatic AB（瑞典）（oemautomatic.se）</t>
+          <t>华沙，自动化目录分销，SKU 量大；OEM Automatic 集团：瑞典 oemautomatic.se（自有品牌，OEM 优先）+ 捷克 oemautomatic.cz，一单谈三国 【关联】同集团另一实体：OEM Automatic AB（瑞典）（oemautomatic.se）；【2026-09-23】Antaira 官方 where-to-buy 名录确认的分销商。波兰分销商。</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">

--- a/客户分级跟进表_2026-09.xlsx
+++ b/客户分级跟进表_2026-09.xlsx
@@ -13,8 +13,8 @@
     <sheet name="说明-评级口径与打法" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'A级-重点好跟进'!$A$1:$AA$89</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'B级-慢慢跟'!$A$1:$X$493</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'A级-重点好跟进'!$A$1:$AA$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'B级-慢慢跟'!$A$1:$X$502</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'C级-难啃'!$A$1:$X$150</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA89"/>
+  <dimension ref="A1:AA92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -10490,8 +10490,335 @@
       <c r="Z89" s="3" t="inlineStr"/>
       <c r="AA89" s="3" t="inlineStr"/>
     </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>Henk Veldkamp</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>荷兰</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Zwolle</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr"/>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MTCRE MTCWE MTCTCE MTCUME MTCIPv6E MTCINE MTCSE MTCSWE MTCEWE</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328XGP-4XS24GT-S</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 顾问名录（电话见名录页）</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr"/>
+      <c r="O90" s="3" t="inlineStr"/>
+      <c r="P90" s="3" t="inlineStr"/>
+      <c r="Q90" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录（mikrotik.com/consultants）收录。荷兰证书最全者之一，持 MTCSWE 交换认证；名录显示其讲授 MTCNA–MTCINE 全部课程。</t>
+        </is>
+      </c>
+      <c r="R90" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S90" s="3" t="inlineStr">
+        <is>
+          <t>有明确交换/供电需求（交换认证 MTCSWE、交换专长），三星重点</t>
+        </is>
+      </c>
+      <c r="T90" s="3" t="inlineStr">
+        <is>
+          <t>MTCSWE 交换认证</t>
+        </is>
+      </c>
+      <c r="U90" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328XGP-4XS24GT-S（24×千兆 + 4×万兆 SFP+，三层）</t>
+        </is>
+      </c>
+      <c r="V90" s="3" t="inlineStr">
+        <is>
+          <t>**L3 硬件卸载（线速转发不占 CPU）**、QinQ、ERPS/MSTP、ACL、静态路由、完整 CLI + SSH + SNMP + 私有 MIB、VLAN 翻译重写</t>
+        </is>
+      </c>
+      <c r="W90" s="3" t="inlineStr">
+        <is>
+          <t>他持有 MTCSWE（MikroTik 交换认证），交换是正式专长——**不用给他做科普**。开口问「你二层环网现在跑什么协议？STP 还是 ERPS？」直接给 CLI 命令对比和转发实测数据</t>
+        </is>
+      </c>
+      <c r="X90" s="3" t="inlineStr">
+        <is>
+          <t>他会拿 Cisco / 锐捷的功能逐条对表，缺一项就被记在小本子上；文档、MIB、CLI 手册必须一次给全；含糊其辞会立刻失去这类技术型客户的信任</t>
+        </is>
+      </c>
+      <c r="Y90" s="3" t="inlineStr"/>
+      <c r="Z90" s="3" t="inlineStr"/>
+      <c r="AA90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Maurice Van Der Grijspaarde</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>荷兰</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Haarlem</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr"/>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MTCRE MTCTCE MTCUME MTCIPv6E MTCINE MTCSE MTCSWE</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328XGP-4XS24GT-S</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 顾问名录</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr"/>
+      <c r="O91" s="3" t="inlineStr"/>
+      <c r="P91" s="3" t="inlineStr"/>
+      <c r="Q91" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录（mikrotik.com/consultants）收录。持 MTCSWE 交换认证。</t>
+        </is>
+      </c>
+      <c r="R91" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S91" s="3" t="inlineStr">
+        <is>
+          <t>有明确交换/供电需求（交换认证 MTCSWE、交换专长），三星重点</t>
+        </is>
+      </c>
+      <c r="T91" s="3" t="inlineStr">
+        <is>
+          <t>MTCSWE 交换认证</t>
+        </is>
+      </c>
+      <c r="U91" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328XGP-4XS24GT-S（24×千兆 + 4×万兆 SFP+，三层）</t>
+        </is>
+      </c>
+      <c r="V91" s="3" t="inlineStr">
+        <is>
+          <t>**L3 硬件卸载（线速转发不占 CPU）**、QinQ、ERPS/MSTP、ACL、静态路由、完整 CLI + SSH + SNMP + 私有 MIB、VLAN 翻译重写</t>
+        </is>
+      </c>
+      <c r="W91" s="3" t="inlineStr">
+        <is>
+          <t>他持有 MTCSWE（MikroTik 交换认证），交换是正式专长——**不用给他做科普**。开口问「你二层环网现在跑什么协议？STP 还是 ERPS？」直接给 CLI 命令对比和转发实测数据</t>
+        </is>
+      </c>
+      <c r="X91" s="3" t="inlineStr">
+        <is>
+          <t>他会拿 Cisco / 锐捷的功能逐条对表，缺一项就被记在小本子上；文档、MIB、CLI 手册必须一次给全；含糊其辞会立刻失去这类技术型客户的信任</t>
+        </is>
+      </c>
+      <c r="Y91" s="3" t="inlineStr"/>
+      <c r="Z91" s="3" t="inlineStr"/>
+      <c r="AA91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>Joost Van De Weijer</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>荷兰</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Bladel</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr"/>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MTCRE MTCWE MTCTCE MTCINE MTCSWE MTCEWE</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328XGP-4XS24GT-S</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 顾问名录</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr"/>
+      <c r="O92" s="3" t="inlineStr"/>
+      <c r="P92" s="3" t="inlineStr"/>
+      <c r="Q92" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录（mikrotik.com/consultants）收录。持 MTCSWE 交换认证。</t>
+        </is>
+      </c>
+      <c r="R92" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S92" s="3" t="inlineStr">
+        <is>
+          <t>有明确交换/供电需求（交换认证 MTCSWE、交换专长），三星重点</t>
+        </is>
+      </c>
+      <c r="T92" s="3" t="inlineStr">
+        <is>
+          <t>MTCSWE 交换认证</t>
+        </is>
+      </c>
+      <c r="U92" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328XGP-4XS24GT-S（24×千兆 + 4×万兆 SFP+，三层）</t>
+        </is>
+      </c>
+      <c r="V92" s="3" t="inlineStr">
+        <is>
+          <t>**L3 硬件卸载（线速转发不占 CPU）**、QinQ、ERPS/MSTP、ACL、静态路由、完整 CLI + SSH + SNMP + 私有 MIB、VLAN 翻译重写</t>
+        </is>
+      </c>
+      <c r="W92" s="3" t="inlineStr">
+        <is>
+          <t>他持有 MTCSWE（MikroTik 交换认证），交换是正式专长——**不用给他做科普**。开口问「你二层环网现在跑什么协议？STP 还是 ERPS？」直接给 CLI 命令对比和转发实测数据</t>
+        </is>
+      </c>
+      <c r="X92" s="3" t="inlineStr">
+        <is>
+          <t>他会拿 Cisco / 锐捷的功能逐条对表，缺一项就被记在小本子上；文档、MIB、CLI 手册必须一次给全；含糊其辞会立刻失去这类技术型客户的信任</t>
+        </is>
+      </c>
+      <c r="Y92" s="3" t="inlineStr"/>
+      <c r="Z92" s="3" t="inlineStr"/>
+      <c r="AA92" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA89"/>
+  <autoFilter ref="A1:AA92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10502,7 +10829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X493"/>
+  <dimension ref="A1:X502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -47652,7 +47979,11 @@
       <c r="N391" s="3" t="inlineStr"/>
       <c r="O391" s="3" t="inlineStr"/>
       <c r="P391" s="3" t="inlineStr"/>
-      <c r="Q391" s="3" t="inlineStr"/>
+      <c r="Q391" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】另经 MikroTik 官方认证顾问名录确认其为认证顾问，持 MTCRE、MTCSE；驻 IJsselstein。</t>
+        </is>
+      </c>
       <c r="R391" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -57349,8 +57680,854 @@
       <c r="W493" s="3" t="inlineStr"/>
       <c r="X493" s="3" t="inlineStr"/>
     </row>
+    <row r="494">
+      <c r="A494" s="3" t="inlineStr">
+        <is>
+          <t>Jasper Hagoort</t>
+        </is>
+      </c>
+      <c r="B494" s="3" t="inlineStr">
+        <is>
+          <t>荷兰</t>
+        </is>
+      </c>
+      <c r="C494" s="3" t="inlineStr">
+        <is>
+          <t>Geertruidenberg</t>
+        </is>
+      </c>
+      <c r="D494" s="3" t="inlineStr"/>
+      <c r="E494" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F494" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MTCRE MTCWE MTCTCE MTCIPv6E MTCINE MTCSE MTCEWE</t>
+        </is>
+      </c>
+      <c r="G494" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H494" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I494" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328GP-4GX24GT-S</t>
+        </is>
+      </c>
+      <c r="J494" s="3" t="inlineStr">
+        <is>
+          <t>+31 6 50462617（可 WhatsApp）</t>
+        </is>
+      </c>
+      <c r="K494" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L494" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M494" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N494" s="3" t="inlineStr"/>
+      <c r="O494" s="3" t="inlineStr"/>
+      <c r="P494" s="3" t="inlineStr"/>
+      <c r="Q494" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录（mikrotik.com/consultants）收录。</t>
+        </is>
+      </c>
+      <c r="R494" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S494" s="3" t="inlineStr">
+        <is>
+          <t>通用分销商信号，无差异化切入点，慢慢跟</t>
+        </is>
+      </c>
+      <c r="T494" s="3" t="inlineStr">
+        <is>
+          <t>待摸底</t>
+        </is>
+      </c>
+      <c r="U494" s="3" t="inlineStr">
+        <is>
+          <t>保持低频联系，等他出现交换机需求信号再跟进</t>
+        </is>
+      </c>
+      <c r="V494" s="3" t="inlineStr"/>
+      <c r="W494" s="3" t="inlineStr"/>
+      <c r="X494" s="3" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="3" t="inlineStr">
+        <is>
+          <t>Michiel Visser</t>
+        </is>
+      </c>
+      <c r="B495" s="3" t="inlineStr">
+        <is>
+          <t>荷兰</t>
+        </is>
+      </c>
+      <c r="C495" s="3" t="inlineStr">
+        <is>
+          <t>Deventer</t>
+        </is>
+      </c>
+      <c r="D495" s="3" t="inlineStr"/>
+      <c r="E495" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F495" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MTCRE MTCWE MTCIPv6E MTCINE MTCSE</t>
+        </is>
+      </c>
+      <c r="G495" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H495" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I495" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328GP-4GX24GT-S</t>
+        </is>
+      </c>
+      <c r="J495" s="3" t="inlineStr">
+        <is>
+          <t>+31 6 29047127</t>
+        </is>
+      </c>
+      <c r="K495" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L495" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M495" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N495" s="3" t="inlineStr"/>
+      <c r="O495" s="3" t="inlineStr"/>
+      <c r="P495" s="3" t="inlineStr"/>
+      <c r="Q495" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录（mikrotik.com/consultants）收录。</t>
+        </is>
+      </c>
+      <c r="R495" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S495" s="3" t="inlineStr">
+        <is>
+          <t>通用分销商信号，无差异化切入点，慢慢跟</t>
+        </is>
+      </c>
+      <c r="T495" s="3" t="inlineStr">
+        <is>
+          <t>待摸底</t>
+        </is>
+      </c>
+      <c r="U495" s="3" t="inlineStr">
+        <is>
+          <t>保持低频联系，等他出现交换机需求信号再跟进</t>
+        </is>
+      </c>
+      <c r="V495" s="3" t="inlineStr"/>
+      <c r="W495" s="3" t="inlineStr"/>
+      <c r="X495" s="3" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="3" t="inlineStr">
+        <is>
+          <t>Corné Van Halteren</t>
+        </is>
+      </c>
+      <c r="B496" s="3" t="inlineStr">
+        <is>
+          <t>荷兰</t>
+        </is>
+      </c>
+      <c r="C496" s="3" t="inlineStr">
+        <is>
+          <t>'s-Hertogenbosch</t>
+        </is>
+      </c>
+      <c r="D496" s="3" t="inlineStr"/>
+      <c r="E496" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F496" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MTCRE</t>
+        </is>
+      </c>
+      <c r="G496" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H496" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I496" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328GP-4GX24GT-S</t>
+        </is>
+      </c>
+      <c r="J496" s="3" t="inlineStr">
+        <is>
+          <t>+31 6 28026574；站点 dael.com</t>
+        </is>
+      </c>
+      <c r="K496" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L496" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M496" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N496" s="3" t="inlineStr"/>
+      <c r="O496" s="3" t="inlineStr"/>
+      <c r="P496" s="3" t="inlineStr"/>
+      <c r="Q496" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录（mikrotik.com/consultants）收录。自述提供 MikroTik 网络规划、实施与管理服务。</t>
+        </is>
+      </c>
+      <c r="R496" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S496" s="3" t="inlineStr">
+        <is>
+          <t>通用分销商信号，无差异化切入点，慢慢跟</t>
+        </is>
+      </c>
+      <c r="T496" s="3" t="inlineStr">
+        <is>
+          <t>待摸底</t>
+        </is>
+      </c>
+      <c r="U496" s="3" t="inlineStr">
+        <is>
+          <t>保持低频联系，等他出现交换机需求信号再跟进</t>
+        </is>
+      </c>
+      <c r="V496" s="3" t="inlineStr"/>
+      <c r="W496" s="3" t="inlineStr"/>
+      <c r="X496" s="3" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="3" t="inlineStr">
+        <is>
+          <t>Aris Vink</t>
+        </is>
+      </c>
+      <c r="B497" s="3" t="inlineStr">
+        <is>
+          <t>荷兰</t>
+        </is>
+      </c>
+      <c r="C497" s="3" t="inlineStr">
+        <is>
+          <t>Zoetermeer</t>
+        </is>
+      </c>
+      <c r="D497" s="3" t="inlineStr"/>
+      <c r="E497" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F497" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MTCRE</t>
+        </is>
+      </c>
+      <c r="G497" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H497" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I497" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328GP-4GX24GT-S</t>
+        </is>
+      </c>
+      <c r="J497" s="3" t="inlineStr">
+        <is>
+          <t>+31 6 17552148；站点 sdc.nl</t>
+        </is>
+      </c>
+      <c r="K497" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L497" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M497" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N497" s="3" t="inlineStr"/>
+      <c r="O497" s="3" t="inlineStr"/>
+      <c r="P497" s="3" t="inlineStr"/>
+      <c r="Q497" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录（mikrotik.com/consultants）收录。名录显示为某 MikroTik 增值总代的售前顾问与认证讲师，帮转售商做设计实施。</t>
+        </is>
+      </c>
+      <c r="R497" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S497" s="3" t="inlineStr">
+        <is>
+          <t>有信号（影响力/渠道）但需先验证需求或联系人不具体</t>
+        </is>
+      </c>
+      <c r="T497" s="3" t="inlineStr">
+        <is>
+          <t>影响力/渠道</t>
+        </is>
+      </c>
+      <c r="U497" s="3" t="inlineStr">
+        <is>
+          <t>寄样机+可讲的案例，让他讲课时用；不谈返点</t>
+        </is>
+      </c>
+      <c r="V497" s="3" t="inlineStr"/>
+      <c r="W497" s="3" t="inlineStr"/>
+      <c r="X497" s="3" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="3" t="inlineStr">
+        <is>
+          <t>Rene Dirks</t>
+        </is>
+      </c>
+      <c r="B498" s="3" t="inlineStr">
+        <is>
+          <t>荷兰</t>
+        </is>
+      </c>
+      <c r="C498" s="3" t="inlineStr">
+        <is>
+          <t>Tilburg</t>
+        </is>
+      </c>
+      <c r="D498" s="3" t="inlineStr"/>
+      <c r="E498" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F498" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MTCRE</t>
+        </is>
+      </c>
+      <c r="G498" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H498" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I498" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328GP-4GX24GT-S</t>
+        </is>
+      </c>
+      <c r="J498" s="3" t="inlineStr">
+        <is>
+          <t>+31 135 470063；站点 gewoon-it.nl</t>
+        </is>
+      </c>
+      <c r="K498" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L498" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M498" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N498" s="3" t="inlineStr"/>
+      <c r="O498" s="3" t="inlineStr"/>
+      <c r="P498" s="3" t="inlineStr"/>
+      <c r="Q498" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录（mikrotik.com/consultants）收录。</t>
+        </is>
+      </c>
+      <c r="R498" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S498" s="3" t="inlineStr">
+        <is>
+          <t>通用分销商信号，无差异化切入点，慢慢跟</t>
+        </is>
+      </c>
+      <c r="T498" s="3" t="inlineStr">
+        <is>
+          <t>待摸底</t>
+        </is>
+      </c>
+      <c r="U498" s="3" t="inlineStr">
+        <is>
+          <t>保持低频联系，等他出现交换机需求信号再跟进</t>
+        </is>
+      </c>
+      <c r="V498" s="3" t="inlineStr"/>
+      <c r="W498" s="3" t="inlineStr"/>
+      <c r="X498" s="3" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="3" t="inlineStr">
+        <is>
+          <t>Rogier Banis</t>
+        </is>
+      </c>
+      <c r="B499" s="3" t="inlineStr">
+        <is>
+          <t>荷兰</t>
+        </is>
+      </c>
+      <c r="C499" s="3" t="inlineStr">
+        <is>
+          <t>Maurik</t>
+        </is>
+      </c>
+      <c r="D499" s="3" t="inlineStr"/>
+      <c r="E499" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F499" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MTCRE MTCINE</t>
+        </is>
+      </c>
+      <c r="G499" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H499" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I499" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328GP-4GX24GT-S</t>
+        </is>
+      </c>
+      <c r="J499" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 顾问名录</t>
+        </is>
+      </c>
+      <c r="K499" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L499" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M499" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N499" s="3" t="inlineStr"/>
+      <c r="O499" s="3" t="inlineStr"/>
+      <c r="P499" s="3" t="inlineStr"/>
+      <c r="Q499" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录（mikrotik.com/consultants）收录。自述 20+ 年 LAN/WAN 经验，含无线点对点/点对多点与流量整形。</t>
+        </is>
+      </c>
+      <c r="R499" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S499" s="3" t="inlineStr">
+        <is>
+          <t>通用分销商信号，无差异化切入点，慢慢跟</t>
+        </is>
+      </c>
+      <c r="T499" s="3" t="inlineStr">
+        <is>
+          <t>待摸底</t>
+        </is>
+      </c>
+      <c r="U499" s="3" t="inlineStr">
+        <is>
+          <t>保持低频联系，等他出现交换机需求信号再跟进</t>
+        </is>
+      </c>
+      <c r="V499" s="3" t="inlineStr"/>
+      <c r="W499" s="3" t="inlineStr"/>
+      <c r="X499" s="3" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="3" t="inlineStr">
+        <is>
+          <t>Roelof Daleboudt</t>
+        </is>
+      </c>
+      <c r="B500" s="3" t="inlineStr">
+        <is>
+          <t>荷兰</t>
+        </is>
+      </c>
+      <c r="C500" s="3" t="inlineStr">
+        <is>
+          <t>Coevorden</t>
+        </is>
+      </c>
+      <c r="D500" s="3" t="inlineStr"/>
+      <c r="E500" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F500" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MTCRE</t>
+        </is>
+      </c>
+      <c r="G500" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H500" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I500" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328GP-4GX24GT-S</t>
+        </is>
+      </c>
+      <c r="J500" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 顾问名录</t>
+        </is>
+      </c>
+      <c r="K500" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L500" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M500" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N500" s="3" t="inlineStr"/>
+      <c r="O500" s="3" t="inlineStr"/>
+      <c r="P500" s="3" t="inlineStr"/>
+      <c r="Q500" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录（mikrotik.com/consultants）收录。</t>
+        </is>
+      </c>
+      <c r="R500" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S500" s="3" t="inlineStr">
+        <is>
+          <t>通用分销商信号，无差异化切入点，慢慢跟</t>
+        </is>
+      </c>
+      <c r="T500" s="3" t="inlineStr">
+        <is>
+          <t>待摸底</t>
+        </is>
+      </c>
+      <c r="U500" s="3" t="inlineStr">
+        <is>
+          <t>保持低频联系，等他出现交换机需求信号再跟进</t>
+        </is>
+      </c>
+      <c r="V500" s="3" t="inlineStr"/>
+      <c r="W500" s="3" t="inlineStr"/>
+      <c r="X500" s="3" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="3" t="inlineStr">
+        <is>
+          <t>Krystof Klima</t>
+        </is>
+      </c>
+      <c r="B501" s="3" t="inlineStr">
+        <is>
+          <t>捷克</t>
+        </is>
+      </c>
+      <c r="C501" s="3" t="inlineStr">
+        <is>
+          <t>Lety</t>
+        </is>
+      </c>
+      <c r="D501" s="3" t="inlineStr"/>
+      <c r="E501" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F501" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MTCRE MTCWE MTCTCE MTCUME MTCIPv6E MTCSE</t>
+        </is>
+      </c>
+      <c r="G501" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H501" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I501" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328GP-4GX24GT-S</t>
+        </is>
+      </c>
+      <c r="J501" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 顾问名录</t>
+        </is>
+      </c>
+      <c r="K501" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L501" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M501" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N501" s="3" t="inlineStr"/>
+      <c r="O501" s="3" t="inlineStr"/>
+      <c r="P501" s="3" t="inlineStr"/>
+      <c r="Q501" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录（mikrotik.com/consultants）收录。自述专长带宽管理与队列、RADIUS、高级防火墙、VPN 与隧道、OSPF/BGP 动态路由。</t>
+        </is>
+      </c>
+      <c r="R501" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S501" s="3" t="inlineStr">
+        <is>
+          <t>有信号（ISP/骨干）但需先验证需求或联系人不具体</t>
+        </is>
+      </c>
+      <c r="T501" s="3" t="inlineStr">
+        <is>
+          <t>ISP/骨干</t>
+        </is>
+      </c>
+      <c r="U501" s="3" t="inlineStr">
+        <is>
+          <t>先小批量试用跑稳定性，备件与 RMA 承诺是关键</t>
+        </is>
+      </c>
+      <c r="V501" s="3" t="inlineStr"/>
+      <c r="W501" s="3" t="inlineStr"/>
+      <c r="X501" s="3" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="3" t="inlineStr">
+        <is>
+          <t>Alexandr Mensenin</t>
+        </is>
+      </c>
+      <c r="B502" s="3" t="inlineStr">
+        <is>
+          <t>捷克</t>
+        </is>
+      </c>
+      <c r="C502" s="3" t="inlineStr">
+        <is>
+          <t>Ostrava</t>
+        </is>
+      </c>
+      <c r="D502" s="3" t="inlineStr"/>
+      <c r="E502" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F502" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MTCRE MTCWE MTCTCE MTCUME MTCIPv6E MTCSE</t>
+        </is>
+      </c>
+      <c r="G502" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H502" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I502" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328GP-4GX24GT-S</t>
+        </is>
+      </c>
+      <c r="J502" s="3" t="inlineStr">
+        <is>
+          <t>+420 608 746 740</t>
+        </is>
+      </c>
+      <c r="K502" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L502" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M502" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N502" s="3" t="inlineStr"/>
+      <c r="O502" s="3" t="inlineStr"/>
+      <c r="P502" s="3" t="inlineStr"/>
+      <c r="Q502" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录（mikrotik.com/consultants）收录。自述含 QoS、高级无线、流量分析、VPN/隧道、PtP/PtMP、QinQ。</t>
+        </is>
+      </c>
+      <c r="R502" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S502" s="3" t="inlineStr">
+        <is>
+          <t>通用分销商信号，无差异化切入点，慢慢跟</t>
+        </is>
+      </c>
+      <c r="T502" s="3" t="inlineStr">
+        <is>
+          <t>待摸底</t>
+        </is>
+      </c>
+      <c r="U502" s="3" t="inlineStr">
+        <is>
+          <t>保持低频联系，等他出现交换机需求信号再跟进</t>
+        </is>
+      </c>
+      <c r="V502" s="3" t="inlineStr"/>
+      <c r="W502" s="3" t="inlineStr"/>
+      <c r="X502" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:X493"/>
+  <autoFilter ref="A1:X502"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/客户分级跟进表_2026-09.xlsx
+++ b/客户分级跟进表_2026-09.xlsx
@@ -13,9 +13,9 @@
     <sheet name="说明-评级口径与打法" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'A级-重点好跟进'!$A$1:$AB$92</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'B级-慢慢跟'!$A$1:$Y$502</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'C级-难啃'!$A$1:$Y$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'A级-重点好跟进'!$A$1:$AB$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'B级-慢慢跟'!$A$1:$Y$510</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'C级-难啃'!$A$1:$Y$151</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB92"/>
+  <dimension ref="A1:AB94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11277,8 +11277,228 @@
       <c r="AA92" s="3" t="inlineStr"/>
       <c r="AB92" s="3" t="inlineStr"/>
     </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Amin Dashti</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr"/>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MTCRE MTCWE MTCTCE MTCINE</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328XGP-4XS24GT-S</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>(949) 385-2171；站点 mikrotikinfo.com</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr"/>
+      <c r="O93" s="3" t="inlineStr"/>
+      <c r="P93" s="3" t="inlineStr"/>
+      <c r="Q93" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录 / 认证培训伙伴收录。自述专长带宽控制、负载均衡、静态/OSPF/BGP 路由、防火墙、VPN、Hotspot、PPPoE。</t>
+        </is>
+      </c>
+      <c r="R93" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S93" s="3" t="inlineStr">
+        <is>
+          <t>有明确交换/供电需求（PoE/监控/门禁），且有具体人直联</t>
+        </is>
+      </c>
+      <c r="T93" s="3" t="inlineStr"/>
+      <c r="U93" s="3" t="inlineStr">
+        <is>
+          <t>PoE/监控/门禁</t>
+        </is>
+      </c>
+      <c r="V93" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328GP-4GX24GT-S（24×千兆 PoE++ + 4×万兆上行）</t>
+        </is>
+      </c>
+      <c r="W93" s="3" t="inlineStr">
+        <is>
+          <t>802.3bt 单口 90W、**PoE 看门狗（摄像头死机自动断电重启，省一趟上门）**、250m 延长供电、端口隔离、整机功率预算足</t>
+        </is>
+      </c>
+      <c r="X93" s="3" t="inlineStr">
+        <is>
+          <t>替他算一笔账：24 个 4K 头全开要多少瓦、满配后还剩多少余量——这是每个做监控的人都踩过的坑，算清楚就赢一半</t>
+        </is>
+      </c>
+      <c r="Y93" s="3" t="inlineStr">
+        <is>
+          <t>**PoE 功率预算和供电稳定性是验收红线**，虚标功率会当场翻车；必须送测、必须给整机功率实测数；部分非标 PoE 相机存在兼容性问题，要先拿他的机型测</t>
+        </is>
+      </c>
+      <c r="Z93" s="3" t="inlineStr"/>
+      <c r="AA93" s="3" t="inlineStr"/>
+      <c r="AB93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>Christopher Fikes</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Silsbee, TX</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr"/>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MTCRE</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328XGP-4XS24GT-S</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>站点 fikesmedia.com</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr"/>
+      <c r="O94" s="3" t="inlineStr"/>
+      <c r="P94" s="3" t="inlineStr"/>
+      <c r="Q94" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录 / 认证培训伙伴收录。自述 20+ 年教育与公共部门网络经验（地方政府 ISP 到大学与 K12），专长含交换、VLAN、无线、VoIP。</t>
+        </is>
+      </c>
+      <c r="R94" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S94" s="3" t="inlineStr">
+        <is>
+          <t>有明确交换/供电需求（交换专长），三星重点</t>
+        </is>
+      </c>
+      <c r="T94" s="3" t="inlineStr"/>
+      <c r="U94" s="3" t="inlineStr">
+        <is>
+          <t>校园/教育</t>
+        </is>
+      </c>
+      <c r="V94" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328GP-4GX24GT-S（PoE 供 AP 与摄像头）</t>
+        </is>
+      </c>
+      <c r="W94" s="3" t="inlineStr">
+        <is>
+          <t>PoE 供 AP / 摄像头 / 门禁、按楼栋或按班级 VLAN 隔离、组播、端口隔离、整机功率足</t>
+        </is>
+      </c>
+      <c r="X94" s="3" t="inlineStr">
+        <is>
+          <t>校园是分期扩建的，问「今年新增几栋楼 / 几个班？」；寒暑假是施工窗口，提前一个季度谈</t>
+        </is>
+      </c>
+      <c r="Y94" s="3" t="inlineStr">
+        <is>
+          <t>校园网常走政府招标或教育局集采，要提前摸清是不是框架协议内；开学季绝对不能出问题，验收极严</t>
+        </is>
+      </c>
+      <c r="Z94" s="3" t="inlineStr"/>
+      <c r="AA94" s="3" t="inlineStr"/>
+      <c r="AB94" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB92"/>
+  <autoFilter ref="A1:AB94"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11289,7 +11509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y502"/>
+  <dimension ref="A1:Y510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -61496,8 +61716,768 @@
       <c r="X502" s="3" t="inlineStr"/>
       <c r="Y502" s="3" t="inlineStr"/>
     </row>
+    <row r="503">
+      <c r="A503" s="3" t="inlineStr">
+        <is>
+          <t>Dan Parrish</t>
+        </is>
+      </c>
+      <c r="B503" s="3" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="C503" s="3" t="inlineStr">
+        <is>
+          <t>Fenton, MO</t>
+        </is>
+      </c>
+      <c r="D503" s="3" t="inlineStr"/>
+      <c r="E503" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F503" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MTCRE MTCWE MTCTCE</t>
+        </is>
+      </c>
+      <c r="G503" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H503" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I503" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328XGP-4XS24GT-S</t>
+        </is>
+      </c>
+      <c r="J503" s="3" t="inlineStr">
+        <is>
+          <t>314-735-0270</t>
+        </is>
+      </c>
+      <c r="K503" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L503" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M503" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N503" s="3" t="inlineStr"/>
+      <c r="O503" s="3" t="inlineStr"/>
+      <c r="P503" s="3" t="inlineStr"/>
+      <c r="Q503" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录 / 认证培训伙伴收录。自述做 **WISP 工程与咨询支持**。</t>
+        </is>
+      </c>
+      <c r="R503" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S503" s="3" t="inlineStr">
+        <is>
+          <t>有信号（ISP/骨干、影响力/渠道）但需先验证需求或联系人不具体</t>
+        </is>
+      </c>
+      <c r="T503" s="3" t="inlineStr"/>
+      <c r="U503" s="3" t="inlineStr">
+        <is>
+          <t>ISP/骨干</t>
+        </is>
+      </c>
+      <c r="V503" s="3" t="inlineStr">
+        <is>
+          <t>先小批量试用跑稳定性，备件与 RMA 承诺是关键</t>
+        </is>
+      </c>
+      <c r="W503" s="3" t="inlineStr"/>
+      <c r="X503" s="3" t="inlineStr"/>
+      <c r="Y503" s="3" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="3" t="inlineStr">
+        <is>
+          <t>Kevin Myers</t>
+        </is>
+      </c>
+      <c r="B504" s="3" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="C504" s="3" t="inlineStr">
+        <is>
+          <t>Flowood, MS</t>
+        </is>
+      </c>
+      <c r="D504" s="3" t="inlineStr"/>
+      <c r="E504" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F504" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MTCNA MTCRE MTCTCE MTCUME MTCSE</t>
+        </is>
+      </c>
+      <c r="G504" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H504" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I504" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328XGP-4XS24GT-S</t>
+        </is>
+      </c>
+      <c r="J504" s="3" t="inlineStr">
+        <is>
+          <t>601-287-3868</t>
+        </is>
+      </c>
+      <c r="K504" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L504" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M504" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N504" s="3" t="inlineStr"/>
+      <c r="O504" s="3" t="inlineStr"/>
+      <c r="P504" s="3" t="inlineStr"/>
+      <c r="Q504" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录 / 认证培训伙伴收录。</t>
+        </is>
+      </c>
+      <c r="R504" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S504" s="3" t="inlineStr">
+        <is>
+          <t>有信号（影响力/渠道）但需先验证需求或联系人不具体</t>
+        </is>
+      </c>
+      <c r="T504" s="3" t="inlineStr"/>
+      <c r="U504" s="3" t="inlineStr">
+        <is>
+          <t>影响力/渠道</t>
+        </is>
+      </c>
+      <c r="V504" s="3" t="inlineStr">
+        <is>
+          <t>寄样机+可讲的案例，让他讲课时用；不谈返点</t>
+        </is>
+      </c>
+      <c r="W504" s="3" t="inlineStr"/>
+      <c r="X504" s="3" t="inlineStr"/>
+      <c r="Y504" s="3" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="3" t="inlineStr">
+        <is>
+          <t>Chris Schiessl</t>
+        </is>
+      </c>
+      <c r="B505" s="3" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="C505" s="3" t="inlineStr">
+        <is>
+          <t>Minot, ND</t>
+        </is>
+      </c>
+      <c r="D505" s="3" t="inlineStr"/>
+      <c r="E505" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F505" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MTCRE MTCTCE</t>
+        </is>
+      </c>
+      <c r="G505" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H505" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I505" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328XGP-4XS24GT-S</t>
+        </is>
+      </c>
+      <c r="J505" s="3" t="inlineStr">
+        <is>
+          <t>701-833-0464 / 701-858-5464</t>
+        </is>
+      </c>
+      <c r="K505" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L505" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M505" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N505" s="3" t="inlineStr"/>
+      <c r="O505" s="3" t="inlineStr"/>
+      <c r="P505" s="3" t="inlineStr"/>
+      <c r="Q505" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录 / 认证培训伙伴收录。</t>
+        </is>
+      </c>
+      <c r="R505" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S505" s="3" t="inlineStr">
+        <is>
+          <t>有信号（影响力/渠道）但需先验证需求或联系人不具体</t>
+        </is>
+      </c>
+      <c r="T505" s="3" t="inlineStr"/>
+      <c r="U505" s="3" t="inlineStr">
+        <is>
+          <t>影响力/渠道</t>
+        </is>
+      </c>
+      <c r="V505" s="3" t="inlineStr">
+        <is>
+          <t>寄样机+可讲的案例，让他讲课时用；不谈返点</t>
+        </is>
+      </c>
+      <c r="W505" s="3" t="inlineStr"/>
+      <c r="X505" s="3" t="inlineStr"/>
+      <c r="Y505" s="3" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="3" t="inlineStr">
+        <is>
+          <t>Martin Sundahl</t>
+        </is>
+      </c>
+      <c r="B506" s="3" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="C506" s="3" t="inlineStr">
+        <is>
+          <t>New Port Richey, FL</t>
+        </is>
+      </c>
+      <c r="D506" s="3" t="inlineStr"/>
+      <c r="E506" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F506" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MTCRE</t>
+        </is>
+      </c>
+      <c r="G506" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H506" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I506" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328XGP-4XS24GT-S</t>
+        </is>
+      </c>
+      <c r="J506" s="3" t="inlineStr">
+        <is>
+          <t>+1 727 505 1534（Skype: sundalez1）</t>
+        </is>
+      </c>
+      <c r="K506" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L506" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M506" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N506" s="3" t="inlineStr"/>
+      <c r="O506" s="3" t="inlineStr"/>
+      <c r="P506" s="3" t="inlineStr"/>
+      <c r="Q506" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录 / 认证培训伙伴收录。</t>
+        </is>
+      </c>
+      <c r="R506" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S506" s="3" t="inlineStr">
+        <is>
+          <t>有信号（影响力/渠道）但需先验证需求或联系人不具体</t>
+        </is>
+      </c>
+      <c r="T506" s="3" t="inlineStr"/>
+      <c r="U506" s="3" t="inlineStr">
+        <is>
+          <t>影响力/渠道</t>
+        </is>
+      </c>
+      <c r="V506" s="3" t="inlineStr">
+        <is>
+          <t>寄样机+可讲的案例，让他讲课时用；不谈返点</t>
+        </is>
+      </c>
+      <c r="W506" s="3" t="inlineStr"/>
+      <c r="X506" s="3" t="inlineStr"/>
+      <c r="Y506" s="3" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="3" t="inlineStr">
+        <is>
+          <t>David Garland</t>
+        </is>
+      </c>
+      <c r="B507" s="3" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="C507" s="3" t="inlineStr">
+        <is>
+          <t>Panora, IA</t>
+        </is>
+      </c>
+      <c r="D507" s="3" t="inlineStr"/>
+      <c r="E507" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F507" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MTCINE</t>
+        </is>
+      </c>
+      <c r="G507" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H507" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I507" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328XGP-4XS24GT-S</t>
+        </is>
+      </c>
+      <c r="J507" s="3" t="inlineStr">
+        <is>
+          <t>641-755-3037</t>
+        </is>
+      </c>
+      <c r="K507" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L507" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M507" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N507" s="3" t="inlineStr"/>
+      <c r="O507" s="3" t="inlineStr"/>
+      <c r="P507" s="3" t="inlineStr"/>
+      <c r="Q507" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录 / 认证培训伙伴收录。</t>
+        </is>
+      </c>
+      <c r="R507" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S507" s="3" t="inlineStr">
+        <is>
+          <t>有信号（影响力/渠道）但需先验证需求或联系人不具体</t>
+        </is>
+      </c>
+      <c r="T507" s="3" t="inlineStr"/>
+      <c r="U507" s="3" t="inlineStr">
+        <is>
+          <t>影响力/渠道</t>
+        </is>
+      </c>
+      <c r="V507" s="3" t="inlineStr">
+        <is>
+          <t>寄样机+可讲的案例，让他讲课时用；不谈返点</t>
+        </is>
+      </c>
+      <c r="W507" s="3" t="inlineStr"/>
+      <c r="X507" s="3" t="inlineStr"/>
+      <c r="Y507" s="3" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="3" t="inlineStr">
+        <is>
+          <t>Hector Prado</t>
+        </is>
+      </c>
+      <c r="B508" s="3" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="C508" s="3" t="inlineStr">
+        <is>
+          <t>La Habra, CA</t>
+        </is>
+      </c>
+      <c r="D508" s="3" t="inlineStr"/>
+      <c r="E508" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F508" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MTCRE</t>
+        </is>
+      </c>
+      <c r="G508" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H508" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I508" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328XGP-4XS24GT-S</t>
+        </is>
+      </c>
+      <c r="J508" s="3" t="inlineStr">
+        <is>
+          <t>+595 974 202030（WhatsApp）</t>
+        </is>
+      </c>
+      <c r="K508" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L508" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M508" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N508" s="3" t="inlineStr"/>
+      <c r="O508" s="3" t="inlineStr"/>
+      <c r="P508" s="3" t="inlineStr"/>
+      <c r="Q508" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录 / 认证培训伙伴收录。名录标注为美国加州，但联系方式为巴拉圭号，国别待核实。</t>
+        </is>
+      </c>
+      <c r="R508" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S508" s="3" t="inlineStr">
+        <is>
+          <t>有信号（影响力/渠道）但需先验证需求或联系人不具体</t>
+        </is>
+      </c>
+      <c r="T508" s="3" t="inlineStr"/>
+      <c r="U508" s="3" t="inlineStr">
+        <is>
+          <t>影响力/渠道</t>
+        </is>
+      </c>
+      <c r="V508" s="3" t="inlineStr">
+        <is>
+          <t>寄样机+可讲的案例，让他讲课时用；不谈返点</t>
+        </is>
+      </c>
+      <c r="W508" s="3" t="inlineStr"/>
+      <c r="X508" s="3" t="inlineStr"/>
+      <c r="Y508" s="3" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="3" t="inlineStr">
+        <is>
+          <t>NCTIK</t>
+        </is>
+      </c>
+      <c r="B509" s="3" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="C509" s="3" t="inlineStr">
+        <is>
+          <t>Raleigh, NC</t>
+        </is>
+      </c>
+      <c r="D509" s="3" t="inlineStr"/>
+      <c r="E509" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F509" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MikroTik 认证培训伙伴</t>
+        </is>
+      </c>
+      <c r="G509" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H509" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I509" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328XGP-4XS24GT-S</t>
+        </is>
+      </c>
+      <c r="J509" s="3" t="inlineStr">
+        <is>
+          <t>Nctik@nctik.com；+1 704 750 9446</t>
+        </is>
+      </c>
+      <c r="K509" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L509" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M509" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N509" s="3" t="inlineStr"/>
+      <c r="O509" s="3" t="inlineStr"/>
+      <c r="P509" s="3" t="inlineStr"/>
+      <c r="Q509" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录 / 认证培训伙伴收录。北卡认证培训机构，开设全部 MTC*E 工程课程，面向网络工程师、ISP 与 WISP。</t>
+        </is>
+      </c>
+      <c r="R509" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S509" s="3" t="inlineStr">
+        <is>
+          <t>有信号（ISP/骨干、影响力/渠道）但需先验证需求或联系人不具体</t>
+        </is>
+      </c>
+      <c r="T509" s="3" t="inlineStr"/>
+      <c r="U509" s="3" t="inlineStr">
+        <is>
+          <t>ISP/骨干</t>
+        </is>
+      </c>
+      <c r="V509" s="3" t="inlineStr">
+        <is>
+          <t>先小批量试用跑稳定性，备件与 RMA 承诺是关键</t>
+        </is>
+      </c>
+      <c r="W509" s="3" t="inlineStr"/>
+      <c r="X509" s="3" t="inlineStr"/>
+      <c r="Y509" s="3" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="3" t="inlineStr">
+        <is>
+          <t>Steve Discher</t>
+        </is>
+      </c>
+      <c r="B510" s="3" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="C510" s="3" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="D510" s="3" t="inlineStr"/>
+      <c r="E510" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F510" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MikroTik 与 Ubiquiti 认证讲师</t>
+        </is>
+      </c>
+      <c r="G510" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H510" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I510" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328XGP-4XS24GT-S</t>
+        </is>
+      </c>
+      <c r="J510" s="3" t="inlineStr">
+        <is>
+          <t>979-314-4431；站点 mywisptraining.com</t>
+        </is>
+      </c>
+      <c r="K510" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L510" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M510" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N510" s="3" t="inlineStr"/>
+      <c r="O510" s="3" t="inlineStr"/>
+      <c r="P510" s="3" t="inlineStr"/>
+      <c r="Q510" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录 / 认证培训伙伴收录。《RouterOS by Example》作者，**自营 WISP 六年以上**，做 WISP 实操培训。</t>
+        </is>
+      </c>
+      <c r="R510" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S510" s="3" t="inlineStr">
+        <is>
+          <t>有信号（ISP/骨干、影响力/渠道）但需先验证需求或联系人不具体</t>
+        </is>
+      </c>
+      <c r="T510" s="3" t="inlineStr"/>
+      <c r="U510" s="3" t="inlineStr">
+        <is>
+          <t>ISP/骨干</t>
+        </is>
+      </c>
+      <c r="V510" s="3" t="inlineStr">
+        <is>
+          <t>先小批量试用跑稳定性，备件与 RMA 承诺是关键</t>
+        </is>
+      </c>
+      <c r="W510" s="3" t="inlineStr"/>
+      <c r="X510" s="3" t="inlineStr"/>
+      <c r="Y510" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y502"/>
+  <autoFilter ref="A1:Y510"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -61508,7 +62488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y150"/>
+  <dimension ref="A1:Y151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -76619,8 +77599,103 @@
       <c r="X150" s="3" t="inlineStr"/>
       <c r="Y150" s="3" t="inlineStr"/>
     </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>Dennis Burgess</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>美国</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Dittmer, MO</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr"/>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>集成商/顾问（MikroTik 认证）</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 认证顾问，持 MTCRE MTCWE MTCTCE MTCSE MTCEWE</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 生态切入</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>LT-S8328XGP-4XS24GT-S</t>
+        </is>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 顾问名录</t>
+        </is>
+      </c>
+      <c r="K151" s="3" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t>未触达</t>
+        </is>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>MikroTik 官方认证顾问名录</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr"/>
+      <c r="O151" s="3" t="inlineStr"/>
+      <c r="P151" s="3" t="inlineStr"/>
+      <c r="Q151" s="3" t="inlineStr">
+        <is>
+          <t>【2026-09-23】MikroTik 官方认证顾问名录 / 认证培训伙伴收录。自述专长路由/OSPF/BGP、带宽管理、Hotspot、PPPoE、点对点无线；**企业级与大型 WISP 工程支持**。美国 WISP 圈资深人士。</t>
+        </is>
+      </c>
+      <c r="R151" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S151" s="3" t="inlineStr">
+        <is>
+          <t>备注含「大型」，决策链长或存在品牌冲突</t>
+        </is>
+      </c>
+      <c r="T151" s="3" t="inlineStr"/>
+      <c r="U151" s="3" t="inlineStr">
+        <is>
+          <t>集团/大公司，决策链长，采购集中</t>
+        </is>
+      </c>
+      <c r="V151" s="3" t="inlineStr">
+        <is>
+          <t>先问清是国别决策还是集团统一采购；找准品类经理而非 CPO</t>
+        </is>
+      </c>
+      <c r="W151" s="3" t="inlineStr"/>
+      <c r="X151" s="3" t="inlineStr"/>
+      <c r="Y151" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y150"/>
+  <autoFilter ref="A1:Y151"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
